--- a/artfynd/A 6198-2025 artfynd.xlsx
+++ b/artfynd/A 6198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87311681</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817384.4615465098</v>
+        <v>817384</v>
       </c>
       <c r="R2" t="n">
-        <v>7313723.080653183</v>
+        <v>7313723</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87311618</v>
+        <v>119627155</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,40 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvavaträskheden, Nb</t>
+          <t>Timmerberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817550.8370597113</v>
+        <v>817212</v>
       </c>
       <c r="R3" t="n">
-        <v>7313858.230934746</v>
+        <v>7313676</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,56 +860,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87311820</v>
+        <v>87311618</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817526.0635736237</v>
+        <v>817551</v>
       </c>
       <c r="R4" t="n">
-        <v>7313838.929725766</v>
+        <v>7313858</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,19 +953,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835196</v>
+        <v>119591979</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,34 +994,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>4404</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmerberget NV, Nb</t>
+          <t>Timmerberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817223.0074877861</v>
+        <v>817091</v>
       </c>
       <c r="R5" t="n">
-        <v>7313741.135288781</v>
+        <v>7313522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,27 +1068,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91835192</v>
+        <v>119591973</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmerberget NV, Nb</t>
+          <t>Timmerberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817238.31246705</v>
+        <v>817132</v>
       </c>
       <c r="R6" t="n">
-        <v>7313662.994008333</v>
+        <v>7313620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,22 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,27 +1169,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119591990</v>
+        <v>119627136</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>817492</v>
+        <v>817371</v>
       </c>
       <c r="R7" t="n">
-        <v>7313785</v>
+        <v>7313813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,12 +1270,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1358,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119591974</v>
+        <v>119627137</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4745</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>817147</v>
+        <v>817091</v>
       </c>
       <c r="R8" t="n">
-        <v>7313642</v>
+        <v>7313597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,12 +1371,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1464,37 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119591975</v>
+        <v>119785942</v>
       </c>
       <c r="B9" t="n">
-        <v>86350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>4412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817350</v>
+        <v>817159</v>
       </c>
       <c r="R9" t="n">
-        <v>7313830</v>
+        <v>7313642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,19 +1466,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1571,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119591973</v>
+        <v>119591974</v>
       </c>
       <c r="B10" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4412</v>
+        <v>4745</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817132</v>
+        <v>817147</v>
       </c>
       <c r="R10" t="n">
-        <v>7313620</v>
+        <v>7313642</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,37 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119694205</v>
+        <v>119785944</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>4745</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817215</v>
+        <v>817159</v>
       </c>
       <c r="R11" t="n">
-        <v>7313677</v>
+        <v>7313642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,12 +1674,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1783,53 +1690,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119694242</v>
+        <v>87311820</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Timmerberget, Nb</t>
+          <t>Kvavaträskheden, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>817296</v>
+        <v>817526</v>
       </c>
       <c r="R12" t="n">
-        <v>7313745</v>
+        <v>7313839</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,12 +1758,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,59 +1772,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119694241</v>
+        <v>119785959</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817189</v>
+        <v>817313</v>
       </c>
       <c r="R13" t="n">
-        <v>7313654</v>
+        <v>7313748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,12 +1876,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1995,37 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119627180</v>
+        <v>119785945</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2035,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817206</v>
+        <v>817480</v>
       </c>
       <c r="R14" t="n">
-        <v>7313672</v>
+        <v>7313755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,12 +1977,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2101,15 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119627136</v>
+        <v>119591982</v>
       </c>
       <c r="B15" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817371</v>
+        <v>817440</v>
       </c>
       <c r="R15" t="n">
-        <v>7313813</v>
+        <v>7313729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,12 +2078,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2207,37 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119627236</v>
+        <v>119627180</v>
       </c>
       <c r="B16" t="n">
-        <v>86350</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>449</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817383</v>
+        <v>817206</v>
       </c>
       <c r="R16" t="n">
-        <v>7313803</v>
+        <v>7313672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,37 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119627137</v>
+        <v>119627151</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2353,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817091</v>
+        <v>817393</v>
       </c>
       <c r="R17" t="n">
-        <v>7313597</v>
+        <v>7313862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,15 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119627151</v>
+        <v>119627152</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>817393</v>
+        <v>817370</v>
       </c>
       <c r="R18" t="n">
-        <v>7313862</v>
+        <v>7313860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,37 +2397,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119627155</v>
+        <v>119694205</v>
       </c>
       <c r="B19" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>817212</v>
+        <v>817215</v>
       </c>
       <c r="R19" t="n">
-        <v>7313676</v>
+        <v>7313677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2631,15 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119627234</v>
+        <v>119694241</v>
       </c>
       <c r="B20" t="n">
-        <v>86350</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,21 +2509,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817390</v>
+        <v>817189</v>
       </c>
       <c r="R20" t="n">
-        <v>7313781</v>
+        <v>7313654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,12 +2583,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2737,15 +2599,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119785957</v>
+        <v>119694242</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817091</v>
+        <v>817296</v>
       </c>
       <c r="R21" t="n">
-        <v>7313578</v>
+        <v>7313745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2843,15 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119785958</v>
+        <v>119785957</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>817142</v>
+        <v>817091</v>
       </c>
       <c r="R22" t="n">
-        <v>7313628</v>
+        <v>7313578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,37 +2801,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119785944</v>
+        <v>119785958</v>
       </c>
       <c r="B23" t="n">
-        <v>91481</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>817159</v>
+        <v>817142</v>
       </c>
       <c r="R23" t="n">
-        <v>7313642</v>
+        <v>7313628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,218 +2895,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>119785942</v>
-      </c>
-      <c r="B24" t="n">
-        <v>87423</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>4412</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Hygrophorus karstenii</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Timmerberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>817159</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7313642</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Nederluleå</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>119785959</v>
-      </c>
-      <c r="B25" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6439</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gulnål</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Timmerberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>817313</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7313748</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Nederluleå</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>

--- a/artfynd/A 6198-2025 artfynd.xlsx
+++ b/artfynd/A 6198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627155</t>
         </is>
       </c>
     </row>
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591973</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627136</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627137</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785942</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785944</t>
         </is>
       </c>
     </row>
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785959</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785945</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119591982</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627180</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627151</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119627152</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694205</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694241</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694242</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785957</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,8 +3009,37 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>